--- a/site/leagues/proliga/2026_2027/xlsx/opponent_shooting_packs/opponent_shooting_pack_BCB.xlsx
+++ b/site/leagues/proliga/2026_2027/xlsx/opponent_shooting_packs/opponent_shooting_pack_BCB.xlsx
@@ -551,9 +551,9 @@
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
@@ -2150,13 +2150,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BCB_A._ROCHA_GOMES</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>BCB_A._GOMES</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>205916</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>A. Rocha Gomes</t>
+          <t>A. Gomes</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2609,9 +2613,9 @@
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
@@ -3936,13 +3940,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>BCB_A._ROCHA_GOMES</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>BCB_A._GOMES</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>205916</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>A. Rocha Gomes</t>
+          <t>A. Gomes</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -4667,9 +4675,9 @@
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
@@ -5772,13 +5780,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>BCB_A._ROCHA_GOMES</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>BCB_A._GOMES</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>205916</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>A. Rocha Gomes</t>
+          <t>A. Gomes</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -6725,9 +6737,9 @@
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
@@ -7578,13 +7590,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BCB_A._ROCHA_GOMES</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>BCB_A._GOMES</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>205916</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>A. Rocha Gomes</t>
+          <t>A. Gomes</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -9415,9 +9431,9 @@
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
@@ -10068,13 +10084,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BCB_A._ROCHA_GOMES</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>BCB_A._GOMES</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>205916</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>A. Rocha Gomes</t>
+          <t>A. Gomes</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -10945,9 +10965,9 @@
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
@@ -11598,13 +11618,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BCB_A._ROCHA_GOMES</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>BCB_A._GOMES</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>205916</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>A. Rocha Gomes</t>
+          <t>A. Gomes</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
